--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,72 +460,72 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.76917</v>
+        <v>16.71889</v>
       </c>
       <c r="D2" t="n">
-        <v>16.93517</v>
+        <v>16.42256</v>
       </c>
       <c r="E2" t="n">
-        <v>16.49132</v>
+        <v>16.51814</v>
       </c>
       <c r="F2" t="n">
-        <v>42.52078</v>
+        <v>41.96897</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05133</v>
+        <v>0.05006</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81391</v>
+        <v>1.79273</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.9036</v>
+        <v>16.8775</v>
       </c>
       <c r="D3" t="n">
-        <v>16.42965</v>
+        <v>16.60814</v>
       </c>
       <c r="E3" t="n">
-        <v>16.46768</v>
+        <v>16.63723</v>
       </c>
       <c r="F3" t="n">
-        <v>42.87419</v>
+        <v>42.45735</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04992</v>
+        <v>0.05076</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79298</v>
+        <v>1.85393</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.69134</v>
+        <v>16.78671</v>
       </c>
       <c r="D4" t="n">
-        <v>16.42579</v>
+        <v>16.62545</v>
       </c>
       <c r="E4" t="n">
-        <v>16.22467</v>
+        <v>16.68609</v>
       </c>
       <c r="F4" t="n">
-        <v>42.02952</v>
+        <v>42.38889</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05009</v>
+        <v>0.05137</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77458</v>
+        <v>1.81793</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.5528</v>
+        <v>16.62408</v>
       </c>
       <c r="D5" t="n">
-        <v>16.72672</v>
+        <v>16.54175</v>
       </c>
       <c r="E5" t="n">
-        <v>16.72421</v>
+        <v>16.60197</v>
       </c>
       <c r="F5" t="n">
-        <v>42.36554</v>
+        <v>42.58785</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04941</v>
+        <v>0.04989</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81203</v>
+        <v>1.78974</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.66973</v>
+        <v>16.83325</v>
       </c>
       <c r="D6" t="n">
-        <v>16.50409</v>
+        <v>16.37802</v>
       </c>
       <c r="E6" t="n">
-        <v>16.76973</v>
+        <v>16.66708</v>
       </c>
       <c r="F6" t="n">
-        <v>43.07241</v>
+        <v>42.2737</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05112</v>
+        <v>0.05096</v>
       </c>
       <c r="H6" t="n">
-        <v>1.75888</v>
+        <v>1.82963</v>
       </c>
     </row>
     <row r="7">
@@ -585,1285 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.55489</v>
+        <v>16.8534</v>
       </c>
       <c r="D7" t="n">
-        <v>16.87821</v>
+        <v>16.68309</v>
       </c>
       <c r="E7" t="n">
-        <v>16.27645</v>
+        <v>16.75202</v>
       </c>
       <c r="F7" t="n">
-        <v>42.2517</v>
+        <v>42.28265</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0506</v>
+        <v>0.05063</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81727</v>
+        <v>1.82031</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.04457</v>
+        <v>16.90868</v>
       </c>
       <c r="D8" t="n">
-        <v>16.43523</v>
+        <v>16.56284</v>
       </c>
       <c r="E8" t="n">
-        <v>16.65829</v>
+        <v>16.73224</v>
       </c>
       <c r="F8" t="n">
-        <v>42.14218</v>
+        <v>42.16321</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05088</v>
+        <v>0.04971</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79509</v>
+        <v>1.84681</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.75321</v>
+        <v>17.12826</v>
       </c>
       <c r="D9" t="n">
-        <v>16.52074</v>
+        <v>16.48158</v>
       </c>
       <c r="E9" t="n">
-        <v>16.82523</v>
+        <v>16.57862</v>
       </c>
       <c r="F9" t="n">
-        <v>42.19198</v>
+        <v>42.40697</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05028</v>
+        <v>0.05047</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8334</v>
+        <v>1.8199</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.25244</v>
+        <v>16.93286</v>
       </c>
       <c r="D10" t="n">
-        <v>16.38345</v>
+        <v>16.40304</v>
       </c>
       <c r="E10" t="n">
-        <v>16.69942</v>
+        <v>16.4891</v>
       </c>
       <c r="F10" t="n">
-        <v>43.37499</v>
+        <v>42.19335</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05019</v>
+        <v>0.04912</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81381</v>
+        <v>1.81358</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.8853</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.52017</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.57147</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42.68006</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.04956</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.82336</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.7392</v>
+        <v>17.14291</v>
       </c>
       <c r="D12" t="n">
-        <v>16.78458</v>
+        <v>16.34519</v>
       </c>
       <c r="E12" t="n">
-        <v>16.47985</v>
+        <v>16.57748</v>
       </c>
       <c r="F12" t="n">
-        <v>42.55944</v>
+        <v>42.37507</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05002</v>
+        <v>0.0495</v>
       </c>
       <c r="H12" t="n">
-        <v>1.77474</v>
+        <v>1.81196</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.77384</v>
+        <v>16.74251</v>
       </c>
       <c r="D13" t="n">
-        <v>16.69159</v>
+        <v>16.44416</v>
       </c>
       <c r="E13" t="n">
-        <v>16.5141</v>
+        <v>16.63482</v>
       </c>
       <c r="F13" t="n">
-        <v>42.49736</v>
+        <v>42.11219</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05064</v>
+        <v>0.05069</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83542</v>
+        <v>1.85334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.85682</v>
+        <v>16.73598</v>
       </c>
       <c r="D14" t="n">
-        <v>16.9352</v>
+        <v>16.15082</v>
       </c>
       <c r="E14" t="n">
-        <v>16.90675</v>
+        <v>16.4959</v>
       </c>
       <c r="F14" t="n">
-        <v>41.72712</v>
+        <v>42.73259</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04999</v>
+        <v>0.05051</v>
       </c>
       <c r="H14" t="n">
-        <v>1.83344</v>
+        <v>1.84428</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.93515</v>
+        <v>16.95659</v>
       </c>
       <c r="D15" t="n">
-        <v>16.53495</v>
+        <v>16.28092</v>
       </c>
       <c r="E15" t="n">
-        <v>16.98108</v>
+        <v>16.65256</v>
       </c>
       <c r="F15" t="n">
-        <v>42.19522</v>
+        <v>41.99882</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05076</v>
+        <v>0.04999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.83279</v>
+        <v>1.81992</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.00311</v>
+        <v>16.72765</v>
       </c>
       <c r="D16" t="n">
-        <v>16.6082</v>
+        <v>16.6537</v>
       </c>
       <c r="E16" t="n">
-        <v>17.05217</v>
+        <v>16.68098</v>
       </c>
       <c r="F16" t="n">
-        <v>42.2677</v>
+        <v>42.37595</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04991</v>
+        <v>0.05191</v>
       </c>
       <c r="H16" t="n">
-        <v>1.82513</v>
+        <v>1.81216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.236</v>
+        <v>16.78771</v>
       </c>
       <c r="D17" t="n">
-        <v>16.75845</v>
+        <v>16.3113</v>
       </c>
       <c r="E17" t="n">
-        <v>16.90969</v>
+        <v>16.70456</v>
       </c>
       <c r="F17" t="n">
-        <v>42.65377</v>
+        <v>42.70754</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0509</v>
+        <v>0.05041</v>
       </c>
       <c r="H17" t="n">
-        <v>1.83328</v>
+        <v>1.82289</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.59547</v>
+        <v>16.60105</v>
       </c>
       <c r="D18" t="n">
-        <v>16.356</v>
+        <v>16.30631</v>
       </c>
       <c r="E18" t="n">
-        <v>16.84157</v>
+        <v>16.38904</v>
       </c>
       <c r="F18" t="n">
-        <v>41.6659</v>
+        <v>42.34644</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05065</v>
+        <v>0.05064</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8164</v>
+        <v>1.87833</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.74059</v>
+        <v>16.96078</v>
       </c>
       <c r="D19" t="n">
-        <v>16.56681</v>
+        <v>16.35325</v>
       </c>
       <c r="E19" t="n">
-        <v>17.27928</v>
+        <v>16.48324</v>
       </c>
       <c r="F19" t="n">
-        <v>42.55961</v>
+        <v>43.06481</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05112</v>
+        <v>0.0514</v>
       </c>
       <c r="H19" t="n">
-        <v>1.83777</v>
+        <v>1.81497</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.03736</v>
+        <v>16.77195</v>
       </c>
       <c r="D20" t="n">
-        <v>16.30143</v>
+        <v>16.41952</v>
       </c>
       <c r="E20" t="n">
-        <v>16.6664</v>
+        <v>16.75457</v>
       </c>
       <c r="F20" t="n">
-        <v>41.06438</v>
+        <v>42.86871</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05125</v>
+        <v>0.05024</v>
       </c>
       <c r="H20" t="n">
-        <v>1.82002</v>
+        <v>1.87005</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>17.07931</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.45423</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.60808</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.9046</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05133</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.80497</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SR Pad 1</t>
+          <t>Unit 21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.73458</v>
+        <v>16.78152</v>
       </c>
       <c r="D22" t="n">
-        <v>15.39817</v>
+        <v>16.31736</v>
       </c>
       <c r="E22" t="n">
-        <v>15.97939</v>
+        <v>16.66093</v>
       </c>
       <c r="F22" t="n">
-        <v>256.06926</v>
+        <v>42.67473</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.05102</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.83465</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.97382</v>
+        <v>16.8715</v>
       </c>
       <c r="D23" t="n">
-        <v>15.49542</v>
+        <v>16.66212</v>
       </c>
       <c r="E23" t="n">
-        <v>15.67253</v>
+        <v>16.75654</v>
       </c>
       <c r="F23" t="n">
-        <v>256.85322</v>
+        <v>43.5287</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05195</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.81867</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 23</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.77248</v>
+        <v>16.90036</v>
       </c>
       <c r="D24" t="n">
-        <v>15.3297</v>
+        <v>16.50949</v>
       </c>
       <c r="E24" t="n">
-        <v>15.82441</v>
+        <v>16.80384</v>
       </c>
       <c r="F24" t="n">
-        <v>255.55392</v>
+        <v>42.14864</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05156</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.80384</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 24</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.51875</v>
+        <v>17.12152</v>
       </c>
       <c r="D25" t="n">
-        <v>15.5446</v>
+        <v>16.70881</v>
       </c>
       <c r="E25" t="n">
-        <v>15.70259</v>
+        <v>17.11963</v>
       </c>
       <c r="F25" t="n">
-        <v>253.80474</v>
+        <v>42.03948</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.05177</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.8034</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 25</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.40115</v>
+        <v>16.62387</v>
       </c>
       <c r="D26" t="n">
-        <v>15.34797</v>
+        <v>16.55108</v>
       </c>
       <c r="E26" t="n">
-        <v>15.69856</v>
+        <v>16.61641</v>
       </c>
       <c r="F26" t="n">
-        <v>254.21599</v>
+        <v>42.55911</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.82375</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 26</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.54797</v>
+        <v>16.7332</v>
       </c>
       <c r="D27" t="n">
-        <v>15.54307</v>
+        <v>16.3865</v>
       </c>
       <c r="E27" t="n">
-        <v>15.57459</v>
+        <v>16.41513</v>
       </c>
       <c r="F27" t="n">
-        <v>255.34845</v>
+        <v>42.54872</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.05052</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.82137</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.72474</v>
+        <v>17.05569</v>
       </c>
       <c r="D28" t="n">
-        <v>15.54481</v>
+        <v>16.64907</v>
       </c>
       <c r="E28" t="n">
-        <v>15.41665</v>
+        <v>16.88497</v>
       </c>
       <c r="F28" t="n">
-        <v>255.33594</v>
+        <v>42.46146</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05022</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.86991</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 28</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.79289</v>
+        <v>16.81741</v>
       </c>
       <c r="D29" t="n">
-        <v>15.6857</v>
+        <v>16.57846</v>
       </c>
       <c r="E29" t="n">
-        <v>15.49571</v>
+        <v>16.6422</v>
       </c>
       <c r="F29" t="n">
-        <v>256.30947</v>
+        <v>41.76863</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.83053</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 29</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.62583</v>
+        <v>16.98444</v>
       </c>
       <c r="D30" t="n">
-        <v>15.62233</v>
+        <v>16.52263</v>
       </c>
       <c r="E30" t="n">
-        <v>15.82641</v>
+        <v>16.97905</v>
       </c>
       <c r="F30" t="n">
-        <v>259.27921</v>
+        <v>43.7548</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05052</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.80504</v>
       </c>
     </row>
     <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>16.84187</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16.76035</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.81129</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42.08956</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.05068</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.84345</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
+          <t>Unit 31</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.90817</v>
+        <v>16.75084</v>
       </c>
       <c r="D32" t="n">
-        <v>16.10088</v>
+        <v>16.48532</v>
       </c>
       <c r="E32" t="n">
-        <v>16.35604</v>
+        <v>16.7443</v>
       </c>
       <c r="F32" t="n">
-        <v>21.30129</v>
+        <v>42.6266</v>
       </c>
       <c r="G32" t="n">
-        <v>33.52413</v>
+        <v>0.05074</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.84892</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 32</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.66866</v>
+        <v>16.88375</v>
       </c>
       <c r="D33" t="n">
-        <v>15.97903</v>
+        <v>16.33816</v>
       </c>
       <c r="E33" t="n">
-        <v>16.56316</v>
+        <v>16.48013</v>
       </c>
       <c r="F33" t="n">
-        <v>22.13658</v>
+        <v>41.8515</v>
       </c>
       <c r="G33" t="n">
-        <v>33.80598</v>
+        <v>0.04966</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.81401</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 33</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.59451</v>
+        <v>16.86859</v>
       </c>
       <c r="D34" t="n">
-        <v>16.00855</v>
+        <v>16.53143</v>
       </c>
       <c r="E34" t="n">
-        <v>16.69821</v>
+        <v>16.57459</v>
       </c>
       <c r="F34" t="n">
-        <v>21.56429</v>
+        <v>42.48246</v>
       </c>
       <c r="G34" t="n">
-        <v>34.06813</v>
+        <v>0.05138</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.81425</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 34</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.76078</v>
+        <v>16.98193</v>
       </c>
       <c r="D35" t="n">
-        <v>16.00423</v>
+        <v>16.51177</v>
       </c>
       <c r="E35" t="n">
-        <v>16.34755</v>
+        <v>16.7293</v>
       </c>
       <c r="F35" t="n">
-        <v>21.08931</v>
+        <v>43.07532</v>
       </c>
       <c r="G35" t="n">
-        <v>34.37291</v>
+        <v>0.05124</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.80711</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 35</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.61686</v>
+        <v>16.50819</v>
       </c>
       <c r="D36" t="n">
-        <v>16.18419</v>
+        <v>16.33098</v>
       </c>
       <c r="E36" t="n">
-        <v>16.38659</v>
+        <v>16.38419</v>
       </c>
       <c r="F36" t="n">
-        <v>21.55806</v>
+        <v>42.40069</v>
       </c>
       <c r="G36" t="n">
-        <v>34.08516</v>
+        <v>0.0502</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.83128</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 36</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.81778</v>
+        <v>16.97577</v>
       </c>
       <c r="D37" t="n">
-        <v>15.71226</v>
+        <v>16.47698</v>
       </c>
       <c r="E37" t="n">
-        <v>16.17029</v>
+        <v>16.64973</v>
       </c>
       <c r="F37" t="n">
-        <v>21.73537</v>
+        <v>41.9731</v>
       </c>
       <c r="G37" t="n">
-        <v>33.62232</v>
+        <v>0.04999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.78021</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>16.46816</v>
-      </c>
-      <c r="D38" t="n">
-        <v>16.22198</v>
-      </c>
-      <c r="E38" t="n">
-        <v>16.38789</v>
-      </c>
-      <c r="F38" t="n">
-        <v>21.96851</v>
-      </c>
-      <c r="G38" t="n">
-        <v>34.82429</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.47036</v>
+        <v>16.7617</v>
       </c>
       <c r="D39" t="n">
-        <v>16.13728</v>
+        <v>15.79352</v>
       </c>
       <c r="E39" t="n">
-        <v>15.9576</v>
+        <v>16.09266</v>
       </c>
       <c r="F39" t="n">
-        <v>21.64324</v>
+        <v>21.81837</v>
       </c>
       <c r="G39" t="n">
-        <v>33.92024</v>
+        <v>34.49432</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.50602</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.97697</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.3873</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.73259</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.98655</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>16.95365</v>
-      </c>
-      <c r="D40" t="n">
-        <v>16.38151</v>
-      </c>
-      <c r="E40" t="n">
-        <v>16.54943</v>
-      </c>
-      <c r="F40" t="n">
-        <v>21.85244</v>
-      </c>
-      <c r="G40" t="n">
-        <v>33.6925</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="C41" t="n">
+        <v>16.83723</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16.03743</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.52563</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22.16283</v>
+      </c>
+      <c r="G41" t="n">
+        <v>34.53719</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Trace 2</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16.9715</v>
+        <v>16.64858</v>
       </c>
       <c r="D42" t="n">
-        <v>15.72101</v>
+        <v>16.18575</v>
       </c>
       <c r="E42" t="n">
-        <v>15.96096</v>
+        <v>16.48518</v>
       </c>
       <c r="F42" t="n">
-        <v>21.95494</v>
+        <v>21.70873</v>
       </c>
       <c r="G42" t="n">
-        <v>33.72295</v>
+        <v>34.38205</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.79816</v>
+        <v>16.48625</v>
       </c>
       <c r="D43" t="n">
-        <v>15.90493</v>
+        <v>15.87235</v>
       </c>
       <c r="E43" t="n">
-        <v>16.58509</v>
+        <v>16.17052</v>
       </c>
       <c r="F43" t="n">
-        <v>21.51394</v>
+        <v>22.04867</v>
       </c>
       <c r="G43" t="n">
-        <v>34.19965</v>
+        <v>34.68435</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.70932</v>
+        <v>16.5761</v>
       </c>
       <c r="D44" t="n">
-        <v>15.51856</v>
+        <v>15.97689</v>
       </c>
       <c r="E44" t="n">
-        <v>16.58397</v>
+        <v>16.28824</v>
       </c>
       <c r="F44" t="n">
-        <v>21.79109</v>
+        <v>21.72714</v>
       </c>
       <c r="G44" t="n">
-        <v>33.83686</v>
+        <v>33.83737</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.69699</v>
+        <v>16.7152</v>
       </c>
       <c r="D45" t="n">
-        <v>16.1599</v>
+        <v>15.87105</v>
       </c>
       <c r="E45" t="n">
-        <v>16.31295</v>
+        <v>16.36274</v>
       </c>
       <c r="F45" t="n">
-        <v>21.47981</v>
+        <v>21.84875</v>
       </c>
       <c r="G45" t="n">
-        <v>33.83566</v>
+        <v>34.27668</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.73826</v>
+        <v>16.85029</v>
       </c>
       <c r="D46" t="n">
-        <v>16.1084</v>
+        <v>16.17624</v>
       </c>
       <c r="E46" t="n">
-        <v>16.46849</v>
+        <v>16.65207</v>
       </c>
       <c r="F46" t="n">
-        <v>22.38259</v>
+        <v>21.47915</v>
       </c>
       <c r="G46" t="n">
-        <v>33.71866</v>
+        <v>34.34006</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.86372</v>
+        <v>16.66263</v>
       </c>
       <c r="D47" t="n">
-        <v>15.82561</v>
+        <v>15.81546</v>
       </c>
       <c r="E47" t="n">
-        <v>16.37836</v>
+        <v>16.61291</v>
       </c>
       <c r="F47" t="n">
-        <v>21.5569</v>
+        <v>21.627</v>
       </c>
       <c r="G47" t="n">
-        <v>34.44965</v>
+        <v>34.93672</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 10</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.73763</v>
+        <v>16.91234</v>
       </c>
       <c r="D48" t="n">
-        <v>16.15727</v>
+        <v>15.99645</v>
       </c>
       <c r="E48" t="n">
-        <v>16.74463</v>
+        <v>16.47587</v>
       </c>
       <c r="F48" t="n">
-        <v>21.78254</v>
+        <v>22.13659</v>
       </c>
       <c r="G48" t="n">
-        <v>33.82783</v>
+        <v>34.40323</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.95991</v>
+        <v>16.6828</v>
       </c>
       <c r="D49" t="n">
-        <v>15.87954</v>
+        <v>15.84262</v>
       </c>
       <c r="E49" t="n">
-        <v>16.40323</v>
+        <v>16.48465</v>
       </c>
       <c r="F49" t="n">
-        <v>22.50421</v>
+        <v>21.4156</v>
       </c>
       <c r="G49" t="n">
-        <v>33.71562</v>
+        <v>33.76526</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16.44008</v>
+        <v>17.01221</v>
       </c>
       <c r="D50" t="n">
-        <v>16.01601</v>
+        <v>15.62702</v>
       </c>
       <c r="E50" t="n">
-        <v>16.43993</v>
+        <v>16.43975</v>
       </c>
       <c r="F50" t="n">
-        <v>21.345</v>
+        <v>21.75056</v>
       </c>
       <c r="G50" t="n">
-        <v>34.50054</v>
+        <v>34.57261</v>
       </c>
     </row>
     <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>16.6308</v>
+      </c>
+      <c r="D51" t="n">
+        <v>15.98801</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.59758</v>
+      </c>
+      <c r="F51" t="n">
+        <v>21.90441</v>
+      </c>
+      <c r="G51" t="n">
+        <v>33.78766</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.61315</v>
+        <v>16.70001</v>
       </c>
       <c r="D52" t="n">
-        <v>1.09874</v>
+        <v>16.1936</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.22083</v>
+      </c>
+      <c r="F52" t="n">
+        <v>22.05111</v>
+      </c>
+      <c r="G52" t="n">
+        <v>34.85</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.60209</v>
+        <v>16.79794</v>
       </c>
       <c r="D53" t="n">
-        <v>1.08958</v>
+        <v>15.87664</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.31157</v>
+      </c>
+      <c r="F53" t="n">
+        <v>22.16892</v>
+      </c>
+      <c r="G53" t="n">
+        <v>33.9816</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.61328</v>
+        <v>16.51602</v>
       </c>
       <c r="D54" t="n">
-        <v>1.14894</v>
+        <v>16.05941</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.30437</v>
+      </c>
+      <c r="F54" t="n">
+        <v>21.60024</v>
+      </c>
+      <c r="G54" t="n">
+        <v>34.73197</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.59939</v>
+        <v>16.64738</v>
       </c>
       <c r="D55" t="n">
-        <v>1.09882</v>
+        <v>16.04367</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.41764</v>
+      </c>
+      <c r="F55" t="n">
+        <v>21.91136</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.58385</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.61759</v>
+        <v>16.843</v>
       </c>
       <c r="D56" t="n">
-        <v>1.1052</v>
+        <v>16.13622</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.14116</v>
+      </c>
+      <c r="F56" t="n">
+        <v>22.0924</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.86156</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.60104</v>
+        <v>16.69154</v>
       </c>
       <c r="D57" t="n">
-        <v>1.10461</v>
+        <v>16.00206</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.25581</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21.51331</v>
+      </c>
+      <c r="G57" t="n">
+        <v>33.9428</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 20</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.61578</v>
+        <v>16.33229</v>
       </c>
       <c r="D58" t="n">
-        <v>1.12454</v>
+        <v>15.96531</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.29633</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22.09778</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.2141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 21</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.60951</v>
+        <v>16.35417</v>
       </c>
       <c r="D59" t="n">
-        <v>1.11355</v>
+        <v>15.77784</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.33905</v>
+      </c>
+      <c r="F59" t="n">
+        <v>21.68585</v>
+      </c>
+      <c r="G59" t="n">
+        <v>33.78019</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 22</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.59467</v>
+        <v>16.61621</v>
       </c>
       <c r="D60" t="n">
-        <v>1.09373</v>
+        <v>16.05509</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.35065</v>
+      </c>
+      <c r="F60" t="n">
+        <v>22.05425</v>
+      </c>
+      <c r="G60" t="n">
+        <v>33.27878</v>
       </c>
     </row>
     <row r="61">
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>16.75151</v>
+      </c>
+      <c r="D61" t="n">
+        <v>15.74624</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.42758</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22.04636</v>
+      </c>
+      <c r="G61" t="n">
+        <v>34.587</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>via 2</t>
+          <t>Unit 24</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.60463</v>
+        <v>16.98277</v>
       </c>
       <c r="D62" t="n">
-        <v>1.12321</v>
+        <v>15.82533</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.35517</v>
+      </c>
+      <c r="F62" t="n">
+        <v>21.94652</v>
+      </c>
+      <c r="G62" t="n">
+        <v>34.30064</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 25</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.60062</v>
+        <v>16.50867</v>
       </c>
       <c r="D63" t="n">
-        <v>1.10512</v>
+        <v>15.45579</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.45249</v>
+      </c>
+      <c r="F63" t="n">
+        <v>21.51821</v>
+      </c>
+      <c r="G63" t="n">
+        <v>35.16736</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 26</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.6190099999999999</v>
+        <v>16.6462</v>
       </c>
       <c r="D64" t="n">
-        <v>1.09859</v>
+        <v>15.93739</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.4739</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.65766</v>
+      </c>
+      <c r="G64" t="n">
+        <v>34.93591</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 27</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.60354</v>
+        <v>16.72211</v>
       </c>
       <c r="D65" t="n">
-        <v>1.13243</v>
+        <v>15.80811</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.31505</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21.72745</v>
+      </c>
+      <c r="G65" t="n">
+        <v>33.91508</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 28</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.61337</v>
+        <v>16.84204</v>
       </c>
       <c r="D66" t="n">
-        <v>1.12094</v>
+        <v>15.61899</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.23567</v>
+      </c>
+      <c r="F66" t="n">
+        <v>21.72958</v>
+      </c>
+      <c r="G66" t="n">
+        <v>34.07034</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 29</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.61205</v>
+        <v>16.73858</v>
       </c>
       <c r="D67" t="n">
-        <v>1.11511</v>
+        <v>16.26786</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.42006</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.58211</v>
+      </c>
+      <c r="G67" t="n">
+        <v>34.06774</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.60599</v>
+        <v>16.77865</v>
       </c>
       <c r="D68" t="n">
-        <v>1.11317</v>
+        <v>16.12205</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.5438</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22.03595</v>
+      </c>
+      <c r="G68" t="n">
+        <v>33.96524</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 31</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.6151</v>
+        <v>16.78777</v>
       </c>
       <c r="D69" t="n">
-        <v>1.11149</v>
+        <v>16.20066</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.58332</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.86658</v>
+      </c>
+      <c r="G69" t="n">
+        <v>34.26842</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 32</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.60971</v>
+        <v>16.72838</v>
       </c>
       <c r="D70" t="n">
-        <v>1.13376</v>
+        <v>16.20948</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.53217</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21.54246</v>
+      </c>
+      <c r="G70" t="n">
+        <v>35.18338</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>16.88335</v>
+      </c>
+      <c r="D71" t="n">
+        <v>15.77083</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.67959</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.84722</v>
+      </c>
+      <c r="G71" t="n">
+        <v>34.3016</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.70551</v>
+      </c>
+      <c r="D72" t="n">
+        <v>15.97772</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.22045</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21.36213</v>
+      </c>
+      <c r="G72" t="n">
+        <v>34.01993</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16.45476</v>
+      </c>
+      <c r="D73" t="n">
+        <v>15.71612</v>
+      </c>
+      <c r="E73" t="n">
+        <v>15.9951</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.6814</v>
+      </c>
+      <c r="G73" t="n">
+        <v>33.5848</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>16.88997</v>
+      </c>
+      <c r="D74" t="n">
+        <v>15.85127</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.19742</v>
+      </c>
+      <c r="F74" t="n">
+        <v>22.13871</v>
+      </c>
+      <c r="G74" t="n">
+        <v>34.44318</v>
       </c>
     </row>
   </sheetData>
